--- a/Projet Le Solitaire 2026 (auto-évaluation _ soutenances).xlsx
+++ b/Projet Le Solitaire 2026 (auto-évaluation _ soutenances).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devoirs\projet python solitaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87008696-1EF8-4B0F-AFAC-8B5D2A67AF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E45362-6C6B-464D-B7F5-A2A4EF34E265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="67">
   <si>
     <t>Soutenances du projet - Le Solitaire</t>
   </si>
@@ -294,6 +294,12 @@
   <si>
     <t>ctypes</t>
   </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>json</t>
+  </si>
 </sst>
 </file>
 
@@ -430,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -520,6 +526,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1117,7 +1126,7 @@
       <c r="AP4" s="15"/>
     </row>
     <row r="5" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="34" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="17"/>
@@ -1264,7 +1273,7 @@
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -1360,7 +1369,7 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
@@ -2072,7 +2081,7 @@
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="20" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -2218,7 +2227,7 @@
       </c>
       <c r="B28" s="15"/>
       <c r="C28" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="15"/>
@@ -2687,7 +2696,9 @@
     <row r="38" spans="1:42" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="26"/>
       <c r="B38" s="15"/>
-      <c r="C38" s="20"/>
+      <c r="C38" s="20" t="s">
+        <v>66</v>
+      </c>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
       <c r="F38" s="15"/>

--- a/Projet Le Solitaire 2026 (auto-évaluation _ soutenances).xlsx
+++ b/Projet Le Solitaire 2026 (auto-évaluation _ soutenances).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devoirs\projet python solitaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E45362-6C6B-464D-B7F5-A2A4EF34E265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040F5365-B7D5-461B-93D2-42E9276ECDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
   <si>
     <t>Soutenances du projet - Le Solitaire</t>
   </si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>ctypes</t>
-  </si>
-  <si>
-    <t>In Progress</t>
   </si>
   <si>
     <t>json</t>
@@ -2081,7 +2078,7 @@
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="20" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15"/>
@@ -2131,7 +2128,7 @@
         <v>44</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="15"/>
@@ -2697,7 +2694,7 @@
       <c r="A38" s="26"/>
       <c r="B38" s="15"/>
       <c r="C38" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>

--- a/Projet Le Solitaire 2026 (auto-évaluation _ soutenances).xlsx
+++ b/Projet Le Solitaire 2026 (auto-évaluation _ soutenances).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Devoirs\projet python solitaire\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040F5365-B7D5-461B-93D2-42E9276ECDB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA3C00A-6645-46BC-9E8E-1442DA639C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="67">
   <si>
     <t>Soutenances du projet - Le Solitaire</t>
   </si>
@@ -297,6 +297,9 @@
   <si>
     <t>json</t>
   </si>
+  <si>
+    <t>In Progress</t>
+  </si>
 </sst>
 </file>
 
@@ -305,7 +308,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dddd\ d\ mmmm"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -394,6 +397,18 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -433,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -514,6 +529,9 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -524,7 +542,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -760,11 +781,11 @@
     <col min="10" max="42" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+    <row r="1" spans="1:42" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="32"/>
+      <c r="B1" s="33"/>
       <c r="C1" s="4">
         <v>1</v>
       </c>
@@ -911,8 +932,8 @@
       <c r="AP1" s="6"/>
     </row>
     <row r="2" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31"/>
-      <c r="B2" s="31"/>
+      <c r="A2" s="32"/>
+      <c r="B2" s="32"/>
       <c r="C2" s="11" t="s">
         <v>21</v>
       </c>
@@ -1031,8 +1052,8 @@
       <c r="AP2" s="12"/>
     </row>
     <row r="3" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="32"/>
       <c r="C3" s="13" t="s">
         <v>57</v>
       </c>
@@ -1077,8 +1098,8 @@
       <c r="AP3" s="15"/>
     </row>
     <row r="4" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="13" t="s">
         <v>58</v>
       </c>
@@ -1123,7 +1144,7 @@
       <c r="AP4" s="15"/>
     </row>
     <row r="5" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="30" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="17"/>
@@ -1366,7 +1387,7 @@
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
@@ -1929,12 +1950,12 @@
       <c r="AP21" s="17"/>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="36" t="s">
         <v>39</v>
       </c>
       <c r="B22" s="15"/>
       <c r="C22" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="15"/>
@@ -2025,12 +2046,12 @@
       <c r="AP23" s="15"/>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="36" t="s">
         <v>41</v>
       </c>
       <c r="B24" s="15"/>
       <c r="C24" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="15"/>
@@ -2171,12 +2192,12 @@
       <c r="AP26" s="15"/>
     </row>
     <row r="27" spans="1:42" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="35" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="15"/>
       <c r="C27" s="20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="15"/>
@@ -2267,12 +2288,12 @@
       <c r="AP28" s="15"/>
     </row>
     <row r="29" spans="1:42" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B29" s="15"/>
       <c r="C29" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="15"/>
@@ -2361,12 +2382,12 @@
       <c r="AP30" s="17"/>
     </row>
     <row r="31" spans="1:42" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="35" t="s">
         <v>49</v>
       </c>
       <c r="B31" s="15"/>
       <c r="C31" s="20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D31" s="15"/>
       <c r="E31" s="15"/>
@@ -2409,12 +2430,12 @@
       <c r="AP31" s="15"/>
     </row>
     <row r="32" spans="1:42" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="35" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="15"/>
       <c r="C32" s="20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="15"/>
@@ -2457,12 +2478,12 @@
       <c r="AP32" s="15"/>
     </row>
     <row r="33" spans="1:42" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="35" t="s">
         <v>51</v>
       </c>
       <c r="B33" s="15"/>
       <c r="C33" s="20" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D33" s="15"/>
       <c r="E33" s="15"/>
@@ -45500,13 +45521,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="32"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -45515,7 +45536,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -45524,26 +45545,26 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
@@ -45552,74 +45573,74 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="10"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
     </row>
     <row r="20" spans="1:1" ht="13.2" x14ac:dyDescent="0.25">
@@ -45648,13 +45669,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="32"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -45663,7 +45684,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -45672,26 +45693,26 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
@@ -45700,58 +45721,58 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="C19" s="1"/>
     </row>
@@ -45779,13 +45800,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="32"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -45794,7 +45815,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -45803,26 +45824,26 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>9</v>
       </c>
@@ -45831,58 +45852,58 @@
       </c>
       <c r="C7" s="1"/>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A8" s="9"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A9" s="9"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A10" s="9"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A11" s="9"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A12" s="9"/>
       <c r="B12" s="10"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A13" s="9"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A15" s="9"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A16" s="9"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A18" s="9"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A19" s="9"/>
       <c r="C19" s="1"/>
     </row>
